--- a/output/pdf_financials_xlsx/NMC.xlsx
+++ b/output/pdf_financials_xlsx/NMC.xlsx
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.122481</v>
+        <v>-0.122481</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.122481</v>
+        <v>-0.122481</v>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0.122481</v>
+        <v>-0.122481</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NMC.xlsx
+++ b/output/pdf_financials_xlsx/NMC.xlsx
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.124275</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.192719</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.1612</v>
       </c>
     </row>
     <row r="13">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.874794</v>
+        <v>-8.999069</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-13.207546</v>
+        <v>-13.400265</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-11.448318</v>
+        <v>-11.609518</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.874794</v>
+        <v>-8.999069</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-13.207546</v>
+        <v>-13.400265</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-11.448318</v>
+        <v>-11.609518</v>
       </c>
     </row>
     <row r="30">
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.399363</v>
+        <v>2.949311</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>12.268091</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.399363</v>
+        <v>2.949311</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>12.268091</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.14626</v>
+        <v>3.596312</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1.992725</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">

--- a/output/pdf_financials_xlsx/NMC.xlsx
+++ b/output/pdf_financials_xlsx/NMC.xlsx
@@ -5846,7 +5846,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
